--- a/public/templates/ar/release-contract.xlsx
+++ b/public/templates/ar/release-contract.xlsx
@@ -492,7 +492,7 @@
         <v>النطاق</v>
       </c>
       <c r="B5" t="str">
-        <v>المرحلة المطلوبة: إعادة التشغيل / التشغيل الظلّي / المساعدة / استقلالية محدودة / توسّع مضبوط</v>
+        <v>المرحلة المطلوبة: المحاكاة بأثر رجعي / التشغيل الموازي / المساعدة / استقلالية محدودة / توسّع مضبوط</v>
       </c>
       <c r="C5" t="str">
         <v/>
